--- a/assets/suivi-devis-depart-fr.xlsx
+++ b/assets/suivi-devis-depart-fr.xlsx
@@ -25,13 +25,13 @@
     <t>Devis acceptés</t>
   </si>
   <si>
-    <t>Montant total TTC</t>
+    <t>Montant total taxes incluses</t>
   </si>
   <si>
     <t>En attente</t>
   </si>
   <si>
-    <t>Montant accepté TTC</t>
+    <t>Montant accepté taxes incluses</t>
   </si>
   <si>
     <t>Refusés</t>
@@ -49,13 +49,13 @@
     <t>Validité (jours)</t>
   </si>
   <si>
-    <t>Montant HT</t>
-  </si>
-  <si>
-    <t>TVA</t>
-  </si>
-  <si>
-    <t>Montant TTC</t>
+    <t>Montant avant taxes</t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Montant taxes incluses</t>
   </si>
   <si>
     <t>Date limite</t>
@@ -608,7 +608,7 @@
         <v>2440</v>
       </c>
       <c r="F8">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
@@ -634,7 +634,7 @@
         <v>1265</v>
       </c>
       <c r="F9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -660,7 +660,7 @@
         <v>1890</v>
       </c>
       <c r="F10">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I10" t="s">
         <v>21</v>
@@ -686,7 +686,7 @@
         <v>246</v>
       </c>
       <c r="F11">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I11" t="s">
         <v>5</v>
@@ -709,7 +709,7 @@
         <v>452.5</v>
       </c>
       <c r="F12">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
@@ -732,7 +732,7 @@
         <v>3200</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I13" t="s">
         <v>5</v>
@@ -755,7 +755,7 @@
         <v>980</v>
       </c>
       <c r="F14">
-        <v>0.055</v>
+        <v>0.13</v>
       </c>
       <c r="I14" t="s">
         <v>21</v>
@@ -778,7 +778,7 @@
         <v>1500</v>
       </c>
       <c r="F15">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I15" t="s">
         <v>5</v>
@@ -801,7 +801,7 @@
         <v>610</v>
       </c>
       <c r="F16">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
@@ -824,7 +824,7 @@
         <v>2150</v>
       </c>
       <c r="F17">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I17" t="s">
         <v>5</v>
